--- a/4.evidence/FCRP/ConsolidationEntries_List_2025Q4.xlsx
+++ b/4.evidence/FCRP/ConsolidationEntries_List_2025Q4.xlsx
@@ -460,6 +460,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -523,7 +524,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>テクノプレシジョン東北の投資相殺</t>
+          <t>デモA東北の投資相殺</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -663,7 +664,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TPトレーディング 少数株主持分</t>
+          <t>デモAトレーディング 少数株主持分</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -742,6 +743,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
